--- a/assets/expense_receipt_template.xlsx
+++ b/assets/expense_receipt_template.xlsx
@@ -1,212 +1,131 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\다운로드\05_출장_여비\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B28FB689-CE57-419B-8887-CDE9A5C125E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$I$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Sheet1'!$A$1:$I$39</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
-  <si>
-    <t>사용자</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>부서명</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>적요</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>사용내역</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>날짜</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>숙박비용</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>합계</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;증빙&gt;</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>사용지역</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>대중교통비</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>출 장 증 빙 서 식</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>내용</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>기술거래이전팀</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color theme="1"/>
       <sz val="20"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color theme="1"/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color theme="1"/>
       <sz val="18"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="9"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color theme="1"/>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color theme="1"/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
+        <fgColor theme="4" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -473,148 +392,342 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+  <cellXfs count="54">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -880,227 +993,231 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J34"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.75" customWidth="1"/>
-    <col min="3" max="3" width="12.625" customWidth="1"/>
-    <col min="4" max="4" width="2.625" customWidth="1"/>
-    <col min="6" max="6" width="7.875" customWidth="1"/>
-    <col min="7" max="7" width="9" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="0.375" customWidth="1"/>
+    <col width="11.375" bestFit="1" customWidth="1" style="39" min="1" max="1"/>
+    <col width="29.75" customWidth="1" style="39" min="2" max="2"/>
+    <col width="12.625" customWidth="1" style="39" min="3" max="3"/>
+    <col width="2.625" customWidth="1" style="39" min="4" max="4"/>
+    <col width="7.875" customWidth="1" style="39" min="6" max="6"/>
+    <col hidden="1" width="9" customWidth="1" style="39" min="7" max="7"/>
+    <col width="0.375" customWidth="1" style="39" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="31.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="38" t="s">
-        <v>10</v>
+    <row r="1" ht="31.5" customHeight="1" s="39">
+      <c r="A1" s="38" t="inlineStr">
+        <is>
+          <t>출 장 증 빙 서 식</t>
+        </is>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-    </row>
-    <row r="2" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-    </row>
-    <row r="3" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
-        <v>0</v>
+    </row>
+    <row r="2" ht="17.25" customHeight="1" s="39" thickBot="1">
+      <c r="A2" s="5" t="n"/>
+      <c r="B2" s="5" t="n"/>
+      <c r="C2" s="5" t="n"/>
+      <c r="D2" s="5" t="n"/>
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="5" t="n"/>
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="5" t="n"/>
+    </row>
+    <row r="3" ht="25.5" customHeight="1" s="39">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="7" t="s">
-        <v>1</v>
+      <c r="B3" s="40" t="n"/>
+      <c r="C3" s="41" t="n"/>
+      <c r="D3" s="41" t="n"/>
+      <c r="E3" s="42" t="n"/>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>부서명</t>
+        </is>
       </c>
-      <c r="G3" s="27" t="s">
-        <v>12</v>
+      <c r="G3" s="27" t="n"/>
+      <c r="H3" s="41" t="n"/>
+      <c r="I3" s="41" t="n"/>
+      <c r="J3" s="42" t="n"/>
+    </row>
+    <row r="4" ht="25.5" customHeight="1" s="39">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>사용지역</t>
+        </is>
       </c>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
-      <c r="J3" s="28"/>
-    </row>
-    <row r="4" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
-        <v>8</v>
+      <c r="B4" s="43" t="n"/>
+      <c r="C4" s="44" t="n"/>
+      <c r="D4" s="44" t="n"/>
+      <c r="E4" s="44" t="n"/>
+      <c r="F4" s="44" t="n"/>
+      <c r="G4" s="44" t="n"/>
+      <c r="H4" s="44" t="n"/>
+      <c r="I4" s="44" t="n"/>
+      <c r="J4" s="45" t="n"/>
+    </row>
+    <row r="5" ht="33.75" customHeight="1" s="39" thickBot="1">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>적요</t>
+        </is>
       </c>
-      <c r="B4" s="34"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-      <c r="J4" s="36"/>
-    </row>
-    <row r="5" spans="1:10" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="10" t="s">
-        <v>2</v>
+      <c r="B5" s="37" t="n"/>
+      <c r="C5" s="44" t="n"/>
+      <c r="D5" s="44" t="n"/>
+      <c r="E5" s="44" t="n"/>
+      <c r="F5" s="44" t="n"/>
+      <c r="G5" s="44" t="n"/>
+      <c r="H5" s="44" t="n"/>
+      <c r="I5" s="44" t="n"/>
+      <c r="J5" s="46" t="n"/>
+    </row>
+    <row r="6" ht="16.5" customHeight="1" s="39" thickBot="1">
+      <c r="A6" s="2" t="n"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
+      <c r="J6" s="3" t="n"/>
+    </row>
+    <row r="7" ht="17.25" customHeight="1" s="39">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>사용내역</t>
+        </is>
       </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="37"/>
-      <c r="I5" s="37"/>
-      <c r="J5" s="37"/>
-    </row>
-    <row r="6" spans="1:10" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-    </row>
-    <row r="7" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A7" s="20" t="s">
-        <v>3</v>
+      <c r="B7" s="33" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
       </c>
-      <c r="B7" s="14" t="s">
-        <v>11</v>
+      <c r="C7" s="27" t="inlineStr">
+        <is>
+          <t>날짜</t>
+        </is>
       </c>
-      <c r="C7" s="27" t="s">
-        <v>4</v>
+      <c r="D7" s="42" t="n"/>
+      <c r="E7" s="27" t="inlineStr">
+        <is>
+          <t>대중교통비</t>
+        </is>
       </c>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27" t="s">
-        <v>9</v>
+      <c r="F7" s="41" t="n"/>
+      <c r="G7" s="42" t="n"/>
+      <c r="H7" s="27" t="inlineStr">
+        <is>
+          <t>숙박비용</t>
+        </is>
       </c>
-      <c r="F7" s="27"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="27" t="s">
-        <v>5</v>
+      <c r="I7" s="41" t="n"/>
+      <c r="J7" s="42" t="n"/>
+    </row>
+    <row r="8" ht="16.5" customHeight="1" s="39">
+      <c r="A8" s="47" t="n"/>
+      <c r="B8" s="12" t="n"/>
+      <c r="C8" s="16" t="n"/>
+      <c r="D8" s="46" t="n"/>
+      <c r="E8" s="48" t="n"/>
+      <c r="F8" s="44" t="n"/>
+      <c r="G8" s="46" t="n"/>
+      <c r="H8" s="48" t="n"/>
+      <c r="I8" s="44" t="n"/>
+      <c r="J8" s="46" t="n"/>
+    </row>
+    <row r="9" ht="16.5" customHeight="1" s="39">
+      <c r="A9" s="47" t="n"/>
+      <c r="B9" s="12" t="n"/>
+      <c r="C9" s="16" t="n"/>
+      <c r="D9" s="46" t="n"/>
+      <c r="E9" s="48" t="n"/>
+      <c r="F9" s="44" t="n"/>
+      <c r="G9" s="46" t="n"/>
+      <c r="H9" s="48" t="n"/>
+      <c r="I9" s="44" t="n"/>
+      <c r="J9" s="46" t="n"/>
+    </row>
+    <row r="10" ht="16.5" customHeight="1" s="39">
+      <c r="A10" s="49" t="n"/>
+      <c r="B10" s="12" t="n"/>
+      <c r="C10" s="16" t="n"/>
+      <c r="D10" s="46" t="n"/>
+      <c r="E10" s="48" t="n"/>
+      <c r="F10" s="44" t="n"/>
+      <c r="G10" s="46" t="n"/>
+      <c r="H10" s="48" t="n"/>
+      <c r="I10" s="44" t="n"/>
+      <c r="J10" s="46" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1" s="39" thickBot="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
       </c>
-      <c r="I7" s="27"/>
-      <c r="J7" s="28"/>
-    </row>
-    <row r="8" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="21"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="25"/>
-      <c r="I8" s="25"/>
-      <c r="J8" s="26"/>
-    </row>
-    <row r="9" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="21"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="25"/>
-      <c r="I9" s="25"/>
-      <c r="J9" s="26"/>
-    </row>
-    <row r="10" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="21"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="25"/>
-      <c r="I10" s="25"/>
-      <c r="J10" s="26"/>
-    </row>
-    <row r="11" spans="1:10" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="6" t="s">
-        <v>6</v>
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="50" t="n"/>
+      <c r="D11" s="51" t="n"/>
+      <c r="E11" s="52" t="n"/>
+      <c r="F11" s="53" t="n"/>
+      <c r="G11" s="51" t="n"/>
+      <c r="H11" s="52" t="n"/>
+      <c r="I11" s="53" t="n"/>
+      <c r="J11" s="51" t="n"/>
+    </row>
+    <row r="13" ht="26.25" customHeight="1" s="39">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>&lt;증빙&gt;</t>
+        </is>
       </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="24"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="24"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="24"/>
-    </row>
-    <row r="13" spans="1:10" ht="26.25" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" s="4"/>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="11"/>
-      <c r="B29" s="11"/>
-    </row>
-    <row r="34" spans="1:10" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="18"/>
-      <c r="B34" s="18"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
-      <c r="I34" s="19"/>
-      <c r="J34" s="19"/>
+      <c r="B13" s="4" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="n"/>
+      <c r="B29" s="11" t="n"/>
+    </row>
+    <row r="34" ht="54.75" customHeight="1" s="39">
+      <c r="A34" s="18" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="H11:J11"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E11:G11"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A34:J34"/>
     <mergeCell ref="B3:E3"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B5:J5"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="H8:J8"/>
     <mergeCell ref="B4:J4"/>
-    <mergeCell ref="B5:J5"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="G3:J3"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="A34:J34"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:G11"/>
-    <mergeCell ref="H11:J11"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="C8:D8"/>
     <mergeCell ref="H10:J10"/>
     <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="G3:J3"/>
     <mergeCell ref="E8:G8"/>
     <mergeCell ref="H9:J9"/>
-    <mergeCell ref="E9:F9"/>
   </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="88" orientation="portrait" verticalDpi="300" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="88" verticalDpi="300"/>
 </worksheet>
 </file>